--- a/diseases/d234/1985-1989.xlsx
+++ b/diseases/d234/1985-1989.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>1</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>1</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>2</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>1</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>1</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>4</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>2</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>6</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>2</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>1</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>2</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>3</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>6</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>5</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>2</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18057,9 +17925,6 @@
       <c r="O90" t="n">
         <v>3</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18450,9 +18315,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18843,9 +18705,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19236,9 +19095,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19629,9 +19485,6 @@
       <c r="O98" t="n">
         <v>1</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20022,9 +19875,6 @@
       <c r="O100" t="n">
         <v>4</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="S100" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20415,9 +20265,6 @@
       <c r="O102" t="n">
         <v>5</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="S102" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20808,9 +20655,6 @@
       <c r="O104" t="n">
         <v>2</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21201,9 +21045,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="S106" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21594,9 +21435,6 @@
       <c r="O108" t="n">
         <v>2</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21987,9 +21825,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="S110" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22380,9 +22215,6 @@
       <c r="O112" t="n">
         <v>1</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="S112" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22773,9 +22605,6 @@
       <c r="O114" t="n">
         <v>1</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="S114" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23166,9 +22995,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="S116" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23559,9 +23385,6 @@
       <c r="O118" t="n">
         <v>1</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="S118" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23951,9 +23774,6 @@
       </c>
       <c r="O120" t="n">
         <v>2</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>0</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>

--- a/diseases/d234/1985-1989.xlsx
+++ b/diseases/d234/1985-1989.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -772,12 +772,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -810,42 +810,42 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -916,29 +916,29 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -998,17 +998,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -1044,42 +1044,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1141,19 +1141,19 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1985-02-01</t>
+          <t>1985-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1985-02</t>
+          <t>1985-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1297,19 +1297,19 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1985-02-01</t>
+          <t>1985-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1985-02</t>
+          <t>1985-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1985-03-01</t>
+          <t>1985-02-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1985-03</t>
+          <t>1985-02</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1985-03-01</t>
+          <t>1985-02-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1985-03</t>
+          <t>1985-02</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1921,19 +1921,19 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1985-04-01</t>
+          <t>1985-03-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1985-04</t>
+          <t>1985-03</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -2077,19 +2077,19 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1985-04-01</t>
+          <t>1985-03-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1985-04</t>
+          <t>1985-03</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -2311,19 +2311,19 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1985-05-01</t>
+          <t>1985-04-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1985-05</t>
+          <t>1985-04</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2467,19 +2467,19 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1985-05-01</t>
+          <t>1985-04-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1985-05</t>
+          <t>1985-04</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1985-06-01</t>
+          <t>1985-05-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1985-06</t>
+          <t>1985-05</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1985-06-01</t>
+          <t>1985-05-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1985-06</t>
+          <t>1985-05</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1985-07-01</t>
+          <t>1985-06-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1985-07</t>
+          <t>1985-06</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1985-07-01</t>
+          <t>1985-06-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1985-07</t>
+          <t>1985-06</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1985-08-01</t>
+          <t>1985-07-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1985-08</t>
+          <t>1985-07</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1985-08-01</t>
+          <t>1985-07-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1985-08</t>
+          <t>1985-07</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1985-09-01</t>
+          <t>1985-08-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1985-09</t>
+          <t>1985-08</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -4027,12 +4027,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1985-09-01</t>
+          <t>1985-08-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1985-09</t>
+          <t>1985-08</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -4261,19 +4261,19 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1985-10-01</t>
+          <t>1985-09-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1985-10</t>
+          <t>1985-09</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -4417,19 +4417,19 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1985-10-01</t>
+          <t>1985-09-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1985-10</t>
+          <t>1985-09</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -4651,19 +4651,19 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1985-11-01</t>
+          <t>1985-10-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1985-11</t>
+          <t>1985-10</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -4807,19 +4807,19 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1985-11-01</t>
+          <t>1985-10-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1985-11</t>
+          <t>1985-10</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -5041,19 +5041,19 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1985-12-01</t>
+          <t>1985-11-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1985-12</t>
+          <t>1985-11</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -5197,19 +5197,19 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1985-12-01</t>
+          <t>1985-11-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1985-12</t>
+          <t>1985-11</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -5431,19 +5431,19 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1986-01-01</t>
+          <t>1985-12-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1986-01</t>
+          <t>1985-12</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -5587,19 +5587,19 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1986-01-01</t>
+          <t>1985-12-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1986-01</t>
+          <t>1985-12</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -5791,12 +5791,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -5821,19 +5821,19 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1986-02-01</t>
+          <t>1986-01-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1986-02</t>
+          <t>1986-01</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -5842,12 +5842,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="AT28" t="n">
@@ -5880,42 +5880,42 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5947,12 +5947,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5977,38 +5977,38 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1986-02-01</t>
+          <t>1986-01-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1986-02</t>
+          <t>1986-01</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="O29" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="AT29" t="n">
@@ -6114,42 +6114,42 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6211,19 +6211,19 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1986-03-01</t>
+          <t>1986-01-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1986-03</t>
+          <t>1986-01</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -6367,19 +6367,19 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1986-03-01</t>
+          <t>1986-01-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1986-03</t>
+          <t>1986-01</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -6601,19 +6601,19 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1986-04-01</t>
+          <t>1986-02-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1986-04</t>
+          <t>1986-02</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -6757,19 +6757,19 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1986-04-01</t>
+          <t>1986-02-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1986-04</t>
+          <t>1986-02</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -6991,19 +6991,19 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1986-05-01</t>
+          <t>1986-03-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1986-05</t>
+          <t>1986-03</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -7147,19 +7147,19 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1986-05-01</t>
+          <t>1986-03-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1986-05</t>
+          <t>1986-03</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -7381,12 +7381,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1986-06-01</t>
+          <t>1986-04-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1986-06</t>
+          <t>1986-04</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1986-06-01</t>
+          <t>1986-04-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1986-06</t>
+          <t>1986-04</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -7771,19 +7771,19 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1986-07-01</t>
+          <t>1986-05-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1986-07</t>
+          <t>1986-05</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -7927,19 +7927,19 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1986-07-01</t>
+          <t>1986-05-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1986-07</t>
+          <t>1986-05</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1986-08-01</t>
+          <t>1986-06-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1986-08</t>
+          <t>1986-06</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1986-08-01</t>
+          <t>1986-06-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1986-08</t>
+          <t>1986-06</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -8551,19 +8551,19 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1986-09-01</t>
+          <t>1986-07-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1986-09</t>
+          <t>1986-07</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -8707,19 +8707,19 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1986-09-01</t>
+          <t>1986-07-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1986-09</t>
+          <t>1986-07</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -8941,19 +8941,19 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1986-10-01</t>
+          <t>1986-08-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1986-10</t>
+          <t>1986-08</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -9097,19 +9097,19 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1986-10-01</t>
+          <t>1986-08-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1986-10</t>
+          <t>1986-08</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -9331,12 +9331,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1986-11-01</t>
+          <t>1986-09-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1986-11</t>
+          <t>1986-09</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1986-11-01</t>
+          <t>1986-09-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1986-11</t>
+          <t>1986-09</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -9721,19 +9721,19 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1986-12-01</t>
+          <t>1986-10-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1986-12</t>
+          <t>1986-10</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -9877,19 +9877,19 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1986-12-01</t>
+          <t>1986-10-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1986-12</t>
+          <t>1986-10</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -10111,12 +10111,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1987-01-01</t>
+          <t>1986-11-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1987-01</t>
+          <t>1986-11</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -10267,12 +10267,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1987-01-01</t>
+          <t>1986-11-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1987-01</t>
+          <t>1986-11</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -10501,19 +10501,19 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1987-02-01</t>
+          <t>1986-12-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>1987-02</t>
+          <t>1986-12</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -10657,19 +10657,19 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1987-02-01</t>
+          <t>1986-12-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>1987-02</t>
+          <t>1986-12</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -10891,19 +10891,19 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1987-03-01</t>
+          <t>1987-01-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>1987-03</t>
+          <t>1987-01</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -10912,12 +10912,12 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -10937,7 +10937,7 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -10950,42 +10950,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11017,12 +11017,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -11047,38 +11047,38 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1987-03-01</t>
+          <t>1987-01-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>1987-03</t>
+          <t>1987-01</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -11088,12 +11088,12 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -11138,17 +11138,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -11184,42 +11184,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11281,19 +11281,19 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>1987-04-01</t>
+          <t>1987-01-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>1987-04</t>
+          <t>1987-01</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -11437,19 +11437,19 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>1987-04-01</t>
+          <t>1987-01-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>1987-04</t>
+          <t>1987-01</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -11671,19 +11671,19 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>1987-05-01</t>
+          <t>1987-02-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>1987-05</t>
+          <t>1987-02</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -11827,19 +11827,19 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>1987-05-01</t>
+          <t>1987-02-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>1987-05</t>
+          <t>1987-02</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -12061,12 +12061,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1987-06-01</t>
+          <t>1987-03-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>1987-06</t>
+          <t>1987-03</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -12217,12 +12217,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>1987-06-01</t>
+          <t>1987-03-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>1987-06</t>
+          <t>1987-03</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -12451,19 +12451,19 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>1987-07-01</t>
+          <t>1987-04-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>1987-07</t>
+          <t>1987-04</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -12607,19 +12607,19 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>1987-07-01</t>
+          <t>1987-04-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>1987-07</t>
+          <t>1987-04</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -12841,12 +12841,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>1987-08-01</t>
+          <t>1987-05-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>1987-08</t>
+          <t>1987-05</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -12997,12 +12997,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>1987-08-01</t>
+          <t>1987-05-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>1987-08</t>
+          <t>1987-05</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -13231,19 +13231,19 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>1987-09-01</t>
+          <t>1987-06-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>1987-09</t>
+          <t>1987-06</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13387,19 +13387,19 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>1987-09-01</t>
+          <t>1987-06-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>1987-09</t>
+          <t>1987-06</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -13621,19 +13621,19 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>1987-10-01</t>
+          <t>1987-07-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>1987-10</t>
+          <t>1987-07</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -13777,19 +13777,19 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>1987-10-01</t>
+          <t>1987-07-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>1987-10</t>
+          <t>1987-07</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O69" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -14011,12 +14011,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>1987-11-01</t>
+          <t>1987-08-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>1987-11</t>
+          <t>1987-08</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>1987-11-01</t>
+          <t>1987-08-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>1987-11</t>
+          <t>1987-08</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -14401,19 +14401,19 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>1987-12-01</t>
+          <t>1987-09-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>1987-12</t>
+          <t>1987-09</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -14557,19 +14557,19 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>1987-12-01</t>
+          <t>1987-09-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>1987-12</t>
+          <t>1987-09</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -14791,19 +14791,19 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>1987-10-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>1988-01</t>
+          <t>1987-10</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O74" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -14947,19 +14947,19 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>1987-10-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>1988-01</t>
+          <t>1987-10</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O75" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -15181,19 +15181,19 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>1988-02-01</t>
+          <t>1987-11-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>1988-02</t>
+          <t>1987-11</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15337,19 +15337,19 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>1988-02-01</t>
+          <t>1987-11-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>1988-02</t>
+          <t>1987-11</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -15571,19 +15571,19 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>1988-03-01</t>
+          <t>1987-12-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>1988-03</t>
+          <t>1987-12</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -15727,19 +15727,19 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>1988-03-01</t>
+          <t>1987-12-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>1988-03</t>
+          <t>1987-12</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -15931,12 +15931,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -15961,19 +15961,19 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>1988-04-01</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>1988-04</t>
+          <t>1988-01</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="O80" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -15982,12 +15982,12 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -16007,7 +16007,7 @@
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="AT80" t="n">
@@ -16020,42 +16020,42 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16087,12 +16087,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -16117,38 +16117,38 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>1988-04-01</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>1988-04</t>
+          <t>1988-01</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="O81" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
@@ -16158,12 +16158,12 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr">
@@ -16208,17 +16208,17 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="AT81" t="n">
@@ -16254,42 +16254,42 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16351,19 +16351,19 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>1988-05-01</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>1988-05</t>
+          <t>1988-01</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O82" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -16507,19 +16507,19 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>1988-05-01</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>1988-05</t>
+          <t>1988-01</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O83" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
@@ -16741,19 +16741,19 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>1988-06-01</t>
+          <t>1988-02-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>1988-06</t>
+          <t>1988-02</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -16897,19 +16897,19 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>1988-06-01</t>
+          <t>1988-02-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>1988-06</t>
+          <t>1988-02</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -17131,19 +17131,19 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>1988-07-01</t>
+          <t>1988-03-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>1988-07</t>
+          <t>1988-03</t>
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -17287,19 +17287,19 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>1988-07-01</t>
+          <t>1988-03-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>1988-07</t>
+          <t>1988-03</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -17521,19 +17521,19 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>1988-08-01</t>
+          <t>1988-04-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>1988-08</t>
+          <t>1988-04</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -17677,19 +17677,19 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>1988-08-01</t>
+          <t>1988-04-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>1988-08</t>
+          <t>1988-04</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -17911,19 +17911,19 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>1988-09-01</t>
+          <t>1988-05-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>1988-09</t>
+          <t>1988-05</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O90" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -18067,19 +18067,19 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>1988-09-01</t>
+          <t>1988-05-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>1988-09</t>
+          <t>1988-05</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O91" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -18301,19 +18301,19 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>1988-10-01</t>
+          <t>1988-06-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>1988-10</t>
+          <t>1988-06</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -18457,19 +18457,19 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>1988-10-01</t>
+          <t>1988-06-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>1988-10</t>
+          <t>1988-06</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -18691,12 +18691,12 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>1988-11-01</t>
+          <t>1988-07-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>1988-11</t>
+          <t>1988-07</t>
         </is>
       </c>
       <c r="N94" t="n">
@@ -18847,12 +18847,12 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>1988-11-01</t>
+          <t>1988-07-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>1988-11</t>
+          <t>1988-07</t>
         </is>
       </c>
       <c r="N95" t="n">
@@ -19081,19 +19081,19 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>1988-12-01</t>
+          <t>1988-08-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>1988-12</t>
+          <t>1988-08</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -19237,19 +19237,19 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>1988-12-01</t>
+          <t>1988-08-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>1988-12</t>
+          <t>1988-08</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -19471,19 +19471,19 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>1989-01-01</t>
+          <t>1988-09-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>1989-01</t>
+          <t>1988-09</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -19627,19 +19627,19 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>1989-01-01</t>
+          <t>1988-09-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>1989-01</t>
+          <t>1988-09</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -19861,19 +19861,19 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>1989-02-01</t>
+          <t>1988-10-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>1989-02</t>
+          <t>1988-10</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -20017,19 +20017,19 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>1989-02-01</t>
+          <t>1988-10-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>1989-02</t>
+          <t>1988-10</t>
         </is>
       </c>
       <c r="N101" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -20251,19 +20251,19 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>1989-03-01</t>
+          <t>1988-11-01</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>1989-03</t>
+          <t>1988-11</t>
         </is>
       </c>
       <c r="N102" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -20407,19 +20407,19 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>1989-03-01</t>
+          <t>1988-11-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>1989-03</t>
+          <t>1988-11</t>
         </is>
       </c>
       <c r="N103" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -20641,19 +20641,19 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>1989-04-01</t>
+          <t>1988-12-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>1989-04</t>
+          <t>1988-12</t>
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -20797,19 +20797,19 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>1989-04-01</t>
+          <t>1988-12-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>1989-04</t>
+          <t>1988-12</t>
         </is>
       </c>
       <c r="N105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -21001,12 +21001,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -21031,19 +21031,19 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>1989-05-01</t>
+          <t>1989-01-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>1989-05</t>
+          <t>1989-01</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -21052,12 +21052,12 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -21077,7 +21077,7 @@
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="AT106" t="n">
@@ -21090,42 +21090,42 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21157,12 +21157,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -21187,38 +21187,38 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>1989-05-01</t>
+          <t>1989-01-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>1989-05</t>
+          <t>1989-01</t>
         </is>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -21228,12 +21228,12 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
@@ -21243,7 +21243,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
@@ -21278,17 +21278,17 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21311,7 +21311,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D83_ANNUAL</t>
         </is>
       </c>
       <c r="AT107" t="n">
@@ -21324,42 +21324,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21421,19 +21421,19 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>1989-06-01</t>
+          <t>1989-01-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>1989-06</t>
+          <t>1989-01</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -21577,19 +21577,19 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>1989-06-01</t>
+          <t>1989-01-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>1989-06</t>
+          <t>1989-01</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -21811,19 +21811,19 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>1989-07-01</t>
+          <t>1989-02-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>1989-07</t>
+          <t>1989-02</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -21967,19 +21967,19 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>1989-07-01</t>
+          <t>1989-02-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>1989-07</t>
+          <t>1989-02</t>
         </is>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -22201,19 +22201,19 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>1989-08-01</t>
+          <t>1989-03-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>1989-08</t>
+          <t>1989-03</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O112" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -22357,19 +22357,19 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>1989-08-01</t>
+          <t>1989-03-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>1989-08</t>
+          <t>1989-03</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O113" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -22591,19 +22591,19 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>1989-09-01</t>
+          <t>1989-04-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>1989-09</t>
+          <t>1989-04</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -22747,19 +22747,19 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>1989-09-01</t>
+          <t>1989-04-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>1989-09</t>
+          <t>1989-04</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -22981,12 +22981,12 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>1989-10-01</t>
+          <t>1989-05-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>1989-10</t>
+          <t>1989-05</t>
         </is>
       </c>
       <c r="N116" t="n">
@@ -23137,12 +23137,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>1989-10-01</t>
+          <t>1989-05-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>1989-10</t>
+          <t>1989-05</t>
         </is>
       </c>
       <c r="N117" t="n">
@@ -23371,19 +23371,19 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>1989-11-01</t>
+          <t>1989-06-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>1989-11</t>
+          <t>1989-06</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -23527,19 +23527,19 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>1989-11-01</t>
+          <t>1989-06-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>1989-11</t>
+          <t>1989-06</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -23761,19 +23761,19 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>1989-12-01</t>
+          <t>1989-07-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>1989-12</t>
+          <t>1989-07</t>
         </is>
       </c>
       <c r="N120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -23917,19 +23917,19 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>1989-12-01</t>
+          <t>1989-07-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>1989-12</t>
+          <t>1989-07</t>
         </is>
       </c>
       <c r="N121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -24088,6 +24088,1956 @@
         </is>
       </c>
       <c r="BC121" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>1989-08-01</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>1989-08</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" t="n">
+        <v>1</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>1989-08-01</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>1989-08</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>1</v>
+      </c>
+      <c r="O123" t="n">
+        <v>1</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Paratyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>1989-09-01</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>1989-09</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>1</v>
+      </c>
+      <c r="O124" t="n">
+        <v>1</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>1989-09-01</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>1989-09</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Paratyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>1989-10-01</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>1989-10</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>1989-10-01</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>1989-10</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Paratyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>1989-11-01</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>1989-11</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>1</v>
+      </c>
+      <c r="O128" t="n">
+        <v>1</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>1989-11-01</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>1989-11</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" t="n">
+        <v>1</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Paratyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>1989-12-01</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>1989-12</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>2</v>
+      </c>
+      <c r="O130" t="n">
+        <v>2</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>1989-12-01</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>1989-12</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>2</v>
+      </c>
+      <c r="O131" t="n">
+        <v>2</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>Paratyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN131" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -24209,7 +26159,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -24219,7 +26169,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -24239,7 +26189,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -24249,7 +26199,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -24271,7 +26221,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>73</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16">
